--- a/reports/draft_diff.xlsx
+++ b/reports/draft_diff.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/denimoll/Files/Programming shits/dt-report-generator/reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C011CF-8043-934A-8D0B-56E297A8FD57}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7D77274-8A36-944C-8324-1BCD009AC0CA}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="34">
   <si>
     <t>№</t>
   </si>
@@ -79,18 +79,12 @@
     <t>Component</t>
   </si>
   <si>
-    <t>Verison</t>
-  </si>
-  <si>
     <t>Report generated by dt-report-generator</t>
   </si>
   <si>
     <t>Dependencies</t>
   </si>
   <si>
-    <t>Direct</t>
-  </si>
-  <si>
     <t>Critical</t>
   </si>
   <si>
@@ -106,9 +100,6 @@
     <t>Unknown</t>
   </si>
   <si>
-    <t>All</t>
-  </si>
-  <si>
     <t>Priority</t>
   </si>
   <si>
@@ -131,6 +122,21 @@
   </si>
   <si>
     <t>Used version (B)</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>All (A)</t>
+  </si>
+  <si>
+    <t>Direct (A)</t>
+  </si>
+  <si>
+    <t>All (B)</t>
+  </si>
+  <si>
+    <t>Direct (B)</t>
   </si>
 </sst>
 </file>
@@ -326,14 +332,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1631,7 +1637,7 @@
     <tableColumn id="3" xr3:uid="{FFC137A4-FB67-3D45-88EB-DD55BF6795F0}" name="Severity" dataDxfId="12"/>
     <tableColumn id="5" xr3:uid="{71E37B58-9C32-4122-AAA1-DCD4E3B3E000}" name="Priority" dataDxfId="11"/>
     <tableColumn id="4" xr3:uid="{1A434919-AB14-964F-9CA9-DD4331C139F6}" name="Component"/>
-    <tableColumn id="6" xr3:uid="{E8635739-AAAF-CA48-B42D-D80511409E7A}" name="Verison"/>
+    <tableColumn id="6" xr3:uid="{E8635739-AAAF-CA48-B42D-D80511409E7A}" name="Version"/>
     <tableColumn id="8" xr3:uid="{EF7CC9FE-A595-4D33-8BA6-E3C0A2BB4CF5}" name="Additional info" dataDxfId="10"/>
     <tableColumn id="7" xr3:uid="{A7109B19-9AED-F943-8363-161AFA0558B1}" name="Analysis state"/>
   </tableColumns>
@@ -1648,7 +1654,7 @@
     <tableColumn id="3" xr3:uid="{1E49701C-9B72-C048-B5EE-A09904F36E9E}" name="Severity" dataDxfId="7"/>
     <tableColumn id="5" xr3:uid="{AE83EF8F-E2A4-894A-88E6-4CACA3B59FB7}" name="Priority" dataDxfId="6"/>
     <tableColumn id="4" xr3:uid="{9ACDEFA5-C187-6C44-8E2E-8AD1EBB176CA}" name="Component"/>
-    <tableColumn id="6" xr3:uid="{AE8B1058-062F-2049-AA95-8C0F9208D4A3}" name="Verison"/>
+    <tableColumn id="6" xr3:uid="{AE8B1058-062F-2049-AA95-8C0F9208D4A3}" name="Version"/>
     <tableColumn id="8" xr3:uid="{91C60B15-FAA4-154C-8BFC-1DEA5A74EA50}" name="Additional info" dataDxfId="5"/>
     <tableColumn id="7" xr3:uid="{E4E04A2A-4A43-594D-BF77-8FA5F7243A84}" name="Analysis state"/>
   </tableColumns>
@@ -1665,7 +1671,7 @@
     <tableColumn id="3" xr3:uid="{5D5DF74C-7B8F-7843-A8BD-E078BF292658}" name="Severity" dataDxfId="2"/>
     <tableColumn id="5" xr3:uid="{365DB20A-7A04-BA40-9A7F-6E468AB2AA38}" name="Priority" dataDxfId="1"/>
     <tableColumn id="4" xr3:uid="{23BC3D5A-9C3D-5348-86F0-F36179146550}" name="Component"/>
-    <tableColumn id="6" xr3:uid="{8B952FD5-FAF5-434C-944B-368E4F19CDA7}" name="Verison"/>
+    <tableColumn id="6" xr3:uid="{8B952FD5-FAF5-434C-944B-368E4F19CDA7}" name="Version"/>
     <tableColumn id="8" xr3:uid="{0A1BDC21-53BA-3B41-8997-A43731375B3B}" name="Additional info" dataDxfId="0"/>
     <tableColumn id="7" xr3:uid="{74B0E1BB-B483-7B4A-842F-570E82F7F203}" name="Analysis state"/>
   </tableColumns>
@@ -1967,11 +1973,11 @@
   <sheetData>
     <row r="1" spans="2:5" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D2" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>29</v>
+      <c r="D2" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.2">
@@ -2023,12 +2029,12 @@
       <c r="E8" s="7"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B10" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
+      <c r="B10" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2067,10 +2073,10 @@
         <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
@@ -2079,7 +2085,7 @@
         <v>9</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -2115,19 +2121,19 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -2163,19 +2169,19 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -2211,19 +2217,19 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -2236,26 +2242,32 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C3FCDA6-20B3-49DC-BEAE-089A40828C61}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="25.83203125" customWidth="1"/>
+    <col min="1" max="5" width="25.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>16</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>18</v>
       </c>
       <c r="B2" s="2">
         <f>COUNTIF('Vulnerable dependencies'!F:F,"critical")+C2</f>
@@ -2265,10 +2277,18 @@
         <f>COUNTIF('Vulnerable dependencies'!F:F,"critical in direct dependency")</f>
         <v>0</v>
       </c>
+      <c r="D2" s="2">
+        <f>COUNTIF('Vulnerable dependencies'!F:F,"critical")+E2</f>
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <f>COUNTIF('Vulnerable dependencies'!F:F,"critical in direct dependency")</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2">
         <f>COUNTIF('Vulnerable dependencies'!F:F,"high")+C3</f>
@@ -2278,10 +2298,18 @@
         <f>COUNTIF('Vulnerable dependencies'!F:F,"high in direct dependency")</f>
         <v>0</v>
       </c>
+      <c r="D3" s="2">
+        <f>COUNTIF('Vulnerable dependencies'!F:F,"high")+E3</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <f>COUNTIF('Vulnerable dependencies'!F:F,"high in direct dependency")</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2">
         <f>COUNTIF('Vulnerable dependencies'!F:F,"medium")+C4</f>
@@ -2291,10 +2319,18 @@
         <f>COUNTIF('Vulnerable dependencies'!F:F,"medium in direct dependency")</f>
         <v>0</v>
       </c>
+      <c r="D4" s="2">
+        <f>COUNTIF('Vulnerable dependencies'!F:F,"medium")+E4</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <f>COUNTIF('Vulnerable dependencies'!F:F,"medium in direct dependency")</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF('Vulnerable dependencies'!F:F,"low")+C5</f>
@@ -2304,10 +2340,18 @@
         <f>COUNTIF('Vulnerable dependencies'!F:F,"low in direct dependency")</f>
         <v>0</v>
       </c>
+      <c r="D5" s="2">
+        <f>COUNTIF('Vulnerable dependencies'!F:F,"low")+E5</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <f>COUNTIF('Vulnerable dependencies'!F:F,"low in direct dependency")</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF('Vulnerable dependencies'!F:F,"unknown")+C6</f>
@@ -2317,8 +2361,17 @@
         <f>COUNTIF('Vulnerable dependencies'!F:F,"unknown in direct dependency")</f>
         <v>0</v>
       </c>
+      <c r="D6" s="2">
+        <f>COUNTIF('Vulnerable dependencies'!F:F,"unknown")+E6</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <f>COUNTIF('Vulnerable dependencies'!F:F,"unknown in direct dependency")</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>